--- a/mlef_pipeline/results/OS_6/HIGH_PDL1/RWD_PYRAD/results.xlsx
+++ b/mlef_pipeline/results/OS_6/HIGH_PDL1/RWD_PYRAD/results.xlsx
@@ -473,7 +473,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.60 ± 0.05</t>
+          <t>0.58 ± 0.05</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -483,7 +483,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.68 ± 0.22</t>
+          <t>0.62 ± 0.20</t>
         </is>
       </c>
       <c r="F2" t="n">
